--- a/data/trans_orig/IP05A02-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05A02-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68539</t>
+          <t>69517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83470</t>
+          <t>82935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80765</t>
+          <t>80440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96268</t>
+          <t>96139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153718</t>
+          <t>154210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175317</t>
+          <t>176122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16576</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>29651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17420</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31342</t>
+          <t>31807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37776</t>
+          <t>36471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56977</t>
+          <t>56001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176752</t>
+          <t>176635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199149</t>
+          <t>199021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192272</t>
+          <t>190937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212413</t>
+          <t>211261</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>375487</t>
+          <t>375973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404809</t>
+          <t>406946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>43408</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63929</t>
+          <t>64459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32224</t>
+          <t>31770</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50593</t>
+          <t>51179</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>81445</t>
+          <t>80173</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108221</t>
+          <t>108574</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14784</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26901</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85062</t>
+          <t>86560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102043</t>
+          <t>102446</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98198</t>
+          <t>98047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114728</t>
+          <t>114373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>189785</t>
+          <t>190536</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>211981</t>
+          <t>212874</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>21020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37371</t>
+          <t>36027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19885</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>35240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45623</t>
+          <t>45348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66833</t>
+          <t>66425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139274</t>
+          <t>138329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158727</t>
+          <t>157475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151693</t>
+          <t>151406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170657</t>
+          <t>171432</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>297597</t>
+          <t>297922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>323782</t>
+          <t>324307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,05%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t>43202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>27183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>45366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59111</t>
+          <t>58489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81869</t>
+          <t>82668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13417</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27353</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>489795</t>
+          <t>489259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>526722</t>
+          <t>524523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>542766</t>
+          <t>542024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>577775</t>
+          <t>577766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1044001</t>
+          <t>1038047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1092227</t>
+          <t>1090345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>122278</t>
+          <t>122655</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>157524</t>
+          <t>155323</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>112878</t>
+          <t>112861</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>144748</t>
+          <t>145459</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>242649</t>
+          <t>244949</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>288683</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42615</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40613</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53542</t>
+          <t>53933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79156</t>
+          <t>79098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116197</t>
+          <t>115766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130167</t>
+          <t>130376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117663</t>
+          <t>116626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131015</t>
+          <t>130901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237712</t>
+          <t>237877</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257690</t>
+          <t>258293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12718</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25734</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>26911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45379</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188195</t>
+          <t>186635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206369</t>
+          <t>206130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210826</t>
+          <t>209550</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>232005</t>
+          <t>231662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>405525</t>
+          <t>406024</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>432646</t>
+          <t>432366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24383</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41117</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>28375</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57863</t>
+          <t>57802</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83921</t>
+          <t>82535</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129060</t>
+          <t>128675</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142392</t>
+          <t>142753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122830</t>
+          <t>123566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138320</t>
+          <t>139116</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>255755</t>
+          <t>256183</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>276833</t>
+          <t>277053</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32044</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>29650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49262</t>
+          <t>48784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16023</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124933</t>
+          <t>124396</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142972</t>
+          <t>142643</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148365</t>
+          <t>148613</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163343</t>
+          <t>163152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>277917</t>
+          <t>278167</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>302735</t>
+          <t>301846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>19164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>35755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26452</t>
+          <t>26340</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35236</t>
+          <t>35953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56947</t>
+          <t>56579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15763</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21117</t>
+          <t>21580</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>575208</t>
+          <t>576110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>608876</t>
+          <t>608635</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>615946</t>
+          <t>617197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>649228</t>
+          <t>649525</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1204146</t>
+          <t>1203438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1250115</t>
+          <t>1249263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77248</t>
+          <t>78182</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107794</t>
+          <t>108026</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>82243</t>
+          <t>81984</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112295</t>
+          <t>110869</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169595</t>
+          <t>167679</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>210366</t>
+          <t>210615</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>34987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31369</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>60244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106277</t>
+          <t>106492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119385</t>
+          <t>119530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102571</t>
+          <t>103764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114949</t>
+          <t>115285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215049</t>
+          <t>214194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231934</t>
+          <t>231458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>20659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>18441</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>35541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178012</t>
+          <t>177903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192285</t>
+          <t>192415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221289</t>
+          <t>222151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238016</t>
+          <t>237781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>403593</t>
+          <t>403994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>426233</t>
+          <t>426220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25622</t>
+          <t>25391</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>30707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31763</t>
+          <t>31483</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52353</t>
+          <t>51149</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>157619</t>
+          <t>156613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>172385</t>
+          <t>172175</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150055</t>
+          <t>151685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>167614</t>
+          <t>168586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>315369</t>
+          <t>313908</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>338009</t>
+          <t>336660</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>12627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>26338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29250</t>
+          <t>29708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30012</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50043</t>
+          <t>50367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>138773</t>
+          <t>139858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154633</t>
+          <t>154301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>144930</t>
+          <t>145410</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159785</t>
+          <t>160142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>289095</t>
+          <t>289751</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310291</t>
+          <t>311048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>26057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27057</t>
+          <t>25743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28960</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>47376</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>596995</t>
+          <t>599072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>626683</t>
+          <t>627971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>638895</t>
+          <t>641013</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>668563</t>
+          <t>668334</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1246679</t>
+          <t>1246999</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1290319</t>
+          <t>1289294</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57032</t>
+          <t>55672</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84465</t>
+          <t>81362</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>61891</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>88419</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123801</t>
+          <t>124140</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>162698</t>
+          <t>161926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29274</t>
+          <t>28829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28154</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48265</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44647</t>
+          <t>44439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52494</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>49023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57262</t>
+          <t>56881</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96573</t>
+          <t>96125</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107792</t>
+          <t>108040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138406</t>
+          <t>138142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149789</t>
+          <t>150110</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153377</t>
+          <t>152606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>168805</t>
+          <t>167816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296124</t>
+          <t>295697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315604</t>
+          <t>315609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23387</t>
+          <t>23514</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15990</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>32700</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>153691</t>
+          <t>153265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>165642</t>
+          <t>165889</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>178203</t>
+          <t>178742</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>198189</t>
+          <t>198800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>337373</t>
+          <t>337261</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>361022</t>
+          <t>360117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29560</t>
+          <t>30043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39279</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158724</t>
+          <t>160046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>253673</t>
+          <t>252644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>270595</t>
+          <t>270824</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>289797</t>
+          <t>290012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>426590</t>
+          <t>421749</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>536788</t>
+          <t>537196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19096</t>
+          <t>19848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114516</t>
+          <t>113079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31169</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145685</t>
+          <t>147729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>691</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>506069</t>
+          <t>498731</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>609467</t>
+          <t>609546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>671444</t>
+          <t>669819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>703641</t>
+          <t>702991</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1183095</t>
+          <t>1190782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1300444</t>
+          <t>1302075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>145553</t>
+          <t>153373</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67091</t>
+          <t>69011</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88985</t>
+          <t>88332</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>210298</t>
+          <t>201352</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27484</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>48426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
